--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -1022,10 +1022,10 @@
         <v>119</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         <v>125</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>83.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -1807,17 +1807,17 @@
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>138</v>
+        <v>84</v>
       </c>
       <c r="C38" s="17" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
         <v>125</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>42.4</v>
+        <v>44</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="C39" s="17" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -1864,23 +1864,23 @@
         <v>125</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>42.4</v>
+        <v>43.2</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="D40" s="18" t="n">
         <v>53</v>
@@ -1906,14 +1906,14 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>132</v>
+        <v>73</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D41" s="18" t="n">
         <v>53</v>
@@ -2368,14 +2368,14 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D55" s="18" t="n">
         <v>39</v>
@@ -2401,17 +2401,17 @@
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -2425,10 +2425,10 @@
         <v>125</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>30.4</v>
+        <v>31.2</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57">
@@ -2870,10 +2870,10 @@
         <v>12</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -2887,10 +2887,10 @@
         <v>125</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71">
@@ -2993,36 +2993,36 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="inlineStr">
+      <c r="A74" s="12" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B74" s="17" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C74" s="17" t="n">
-        <v>786</v>
-      </c>
-      <c r="D74" s="18" t="n">
-        <v>404</v>
-      </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="B74" s="13" t="n">
+        <v>1191</v>
+      </c>
+      <c r="C74" s="13" t="n">
+        <v>771</v>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F74" s="17" t="n">
+      <c r="F74" s="13" t="n">
         <v>2000</v>
       </c>
-      <c r="G74" s="17" t="n">
+      <c r="G74" s="13" t="n">
         <v>833.3333333333334</v>
       </c>
-      <c r="H74" s="19" t="n">
-        <v>48.48</v>
+      <c r="H74" s="15" t="n">
+        <v>50.4</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>429.3333333333334</v>
+        <v>413.3333333333334</v>
       </c>
     </row>
     <row r="75">
@@ -3035,10 +3035,10 @@
         <v>430</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>250</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>148.8</v>
+        <v>149.2</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3134,10 +3134,10 @@
         <v>301</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>250</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>106.4</v>
+        <v>106.8</v>
       </c>
       <c r="I78" s="6" t="n">
         <v>0</v>
@@ -3200,10 +3200,10 @@
         <v>285</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         <v>250</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>94.8</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81">
@@ -3233,10 +3233,10 @@
         <v>451</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         <v>250</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>83.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82">
@@ -3332,10 +3332,10 @@
         <v>341</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
@@ -3349,10 +3349,10 @@
         <v>250</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="85">
@@ -3398,10 +3398,10 @@
         <v>166</v>
       </c>
       <c r="C86" s="17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         <v>250</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87">
@@ -4000,10 +4000,10 @@
         <v>119</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -4017,10 +4017,10 @@
         <v>125</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>83.2</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -4785,17 +4785,17 @@
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C38" s="17" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -4809,26 +4809,26 @@
         <v>125</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>42.4</v>
+        <v>44</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="C39" s="17" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -4842,23 +4842,23 @@
         <v>125</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>42.4</v>
+        <v>43.2</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="D40" s="18" t="n">
         <v>53</v>
@@ -4884,14 +4884,14 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D41" s="18" t="n">
         <v>53</v>
@@ -5346,14 +5346,14 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D55" s="18" t="n">
         <v>39</v>
@@ -5379,17 +5379,17 @@
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -5403,10 +5403,10 @@
         <v>125</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>30.4</v>
+        <v>31.2</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="57">
@@ -5848,10 +5848,10 @@
         <v>12</v>
       </c>
       <c r="C70" s="17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" s="18" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -5865,10 +5865,10 @@
         <v>125</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71">
@@ -6054,10 +6054,10 @@
         <v>430</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>250</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>148.8</v>
+        <v>149.2</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6153,10 +6153,10 @@
         <v>301</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>250</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>106.4</v>
+        <v>106.8</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>285</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         <v>250</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>94.8</v>
+        <v>95.19999999999999</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -6252,10 +6252,10 @@
         <v>451</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -6269,10 +6269,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>83.59999999999999</v>
+        <v>84.8</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -6351,10 +6351,10 @@
         <v>341</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>250</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>57.99999999999999</v>
+        <v>58.8</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -6417,10 +6417,10 @@
         <v>166</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
         <v>250</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>46</v>
+        <v>45.6</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -6614,36 +6614,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
-        <v>1190</v>
-      </c>
-      <c r="C2" s="17" t="n">
-        <v>786</v>
-      </c>
-      <c r="D2" s="18" t="n">
-        <v>404</v>
-      </c>
-      <c r="E2" s="16" t="inlineStr">
+      <c r="B2" s="13" t="n">
+        <v>1191</v>
+      </c>
+      <c r="C2" s="13" t="n">
+        <v>771</v>
+      </c>
+      <c r="D2" s="14" t="n">
+        <v>420</v>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F2" s="17" t="n">
+      <c r="F2" s="13" t="n">
         <v>2000</v>
       </c>
-      <c r="G2" s="17" t="n">
+      <c r="G2" s="13" t="n">
         <v>833.3333333333334</v>
       </c>
-      <c r="H2" s="19" t="n">
-        <v>48.48</v>
+      <c r="H2" s="15" t="n">
+        <v>50.4</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>429.3333333333334</v>
+        <v>413.3333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -7068,10 +7068,10 @@
         <v>12</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
@@ -7085,10 +7085,10 @@
         <v>125</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6">
@@ -7208,10 +7208,10 @@
         <v>430</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>250</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>148.8</v>
+        <v>149.2</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>12802</v>
+        <v>12803</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>4889</v>
+        <v>4859</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>7913</v>
+        <v>7944</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -725,10 +725,10 @@
         <v>167</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -742,7 +742,7 @@
         <v>125</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>112</v>
+        <v>111.2</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -850,17 +850,17 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>198</v>
+        <v>141</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -874,26 +874,26 @@
         <v>125</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>94.39999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
         <v>125</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>92.80000000000001</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>18</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -940,26 +940,26 @@
         <v>125</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>90.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -973,26 +973,26 @@
         <v>125</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>88.8</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1006,26 +1006,26 @@
         <v>125</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         <v>125</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>85.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C21" s="13" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -1270,10 +1270,10 @@
         <v>125</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>78.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
@@ -1283,13 +1283,13 @@
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C22" s="13" t="n">
         <v>53</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1303,26 +1303,26 @@
         <v>125</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>75.2</v>
+        <v>79.2</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1336,26 +1336,26 @@
         <v>125</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>72</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1369,26 +1369,26 @@
         <v>125</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>70.39999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1402,26 +1402,26 @@
         <v>125</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>61.6</v>
+        <v>70.39999999999999</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>109</v>
+        <v>244</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>34</v>
+        <v>158</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>125</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         <v>125</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>58.4</v>
+        <v>68.8</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         <v>125</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1534,26 +1534,26 @@
         <v>125</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>54.40000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,26 +1567,26 @@
         <v>125</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>52.8</v>
+        <v>57.59999999999999</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,26 +1600,26 @@
         <v>125</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>52.8</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>224</v>
+        <v>84</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -1633,26 +1633,26 @@
         <v>125</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>52.8</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1666,125 +1666,125 @@
         <v>125</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>51.2</v>
+        <v>52.8</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D34" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H34" s="15" t="n">
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H35" s="15" t="n">
         <v>51.2</v>
       </c>
-      <c r="I34" s="11" t="n">
+      <c r="I35" s="11" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Lakshminarasimhapuram B.O</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="n">
-        <v>71</v>
-      </c>
-      <c r="C35" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D35" s="18" t="n">
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Komaravolu B.O</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>148</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="I36" s="11" t="n">
         <v>62</v>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G35" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Unikili B.O</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="n">
-        <v>67</v>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G36" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H36" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I36" s="11" t="n">
-        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C37" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
@@ -1798,26 +1798,26 @@
         <v>125</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>47.2</v>
+        <v>49.6</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C38" s="17" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -1831,26 +1831,26 @@
         <v>125</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="C39" s="17" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -1864,26 +1864,26 @@
         <v>125</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>43.2</v>
+        <v>44</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
@@ -1897,23 +1897,23 @@
         <v>125</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>42.4</v>
+        <v>43.2</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D41" s="18" t="n">
         <v>53</v>
@@ -1939,17 +1939,17 @@
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -1963,26 +1963,26 @@
         <v>125</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>42.4</v>
+        <v>41.6</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -1996,26 +1996,26 @@
         <v>125</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -2029,23 +2029,23 @@
         <v>125</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>40.8</v>
+        <v>37.6</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="D45" s="18" t="n">
         <v>47</v>
@@ -2071,14 +2071,14 @@
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="D46" s="18" t="n">
         <v>47</v>
@@ -2104,17 +2104,17 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Addada B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -2128,23 +2128,23 @@
         <v>125</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>36.8</v>
+        <v>36</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D48" s="18" t="n">
         <v>45</v>
@@ -2170,14 +2170,14 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D49" s="18" t="n">
         <v>44</v>
@@ -2203,14 +2203,14 @@
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D50" s="18" t="n">
         <v>44</v>
@@ -2236,17 +2236,17 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -2260,26 +2260,26 @@
         <v>125</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -2293,23 +2293,23 @@
         <v>125</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D53" s="18" t="n">
         <v>42</v>
@@ -2335,17 +2335,17 @@
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         <v>125</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>32</v>
+        <v>33.6</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
@@ -2434,17 +2434,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -2458,26 +2458,26 @@
         <v>125</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>27.2</v>
+        <v>31.2</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,26 +2491,26 @@
         <v>125</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>24.8</v>
+        <v>27.2</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2524,59 +2524,59 @@
         <v>125</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D60" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="H60" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F60" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G60" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H60" s="19" t="n">
-        <v>19.2</v>
-      </c>
       <c r="I60" s="11" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2590,23 +2590,23 @@
         <v>125</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="D62" s="18" t="n">
         <v>22</v>
@@ -2632,17 +2632,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -2656,26 +2656,26 @@
         <v>125</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>16</v>
+        <v>17.6</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
         <v>125</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>13.6</v>
+        <v>16</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2722,26 +2722,26 @@
         <v>125</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>12.8</v>
+        <v>13.6</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2755,23 +2755,23 @@
         <v>125</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>10.4</v>
+        <v>12.8</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D67" s="18" t="n">
         <v>13</v>
@@ -2966,13 +2966,13 @@
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C73" s="17" t="n">
         <v>121</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-39</v>
+        <v>-29</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -2986,10 +2986,10 @@
         <v>125</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-31.2</v>
+        <v>-23.2</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         <v>833.3333333333334</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>50.4</v>
+        <v>51.23999999999999</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>413.3333333333334</v>
+        <v>406.3333333333334</v>
       </c>
     </row>
     <row r="75">
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>48</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>250</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>127.6</v>
+        <v>128.4</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>34</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>250</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>106.8</v>
+        <v>107.2</v>
       </c>
       <c r="I78" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>67</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>250</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>103.6</v>
+        <v>104.4</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>0</v>
@@ -3197,13 +3197,13 @@
         </is>
       </c>
       <c r="B80" s="8" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C80" s="8" t="n">
         <v>47</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         <v>250</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>95.19999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         <v>250</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>84.8</v>
+        <v>84.39999999999999</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82">
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C88" s="17" t="n">
         <v>126</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
         <v>250</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="89">
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C89" s="17" t="n">
         <v>56</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>250</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3703,10 +3703,10 @@
         <v>167</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>125</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>112</v>
+        <v>111.2</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -3828,17 +3828,17 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>198</v>
+        <v>141</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3852,26 +3852,26 @@
         <v>125</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>94.39999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -3885,10 +3885,10 @@
         <v>125</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>92.80000000000001</v>
+        <v>94.39999999999999</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -3898,13 +3898,13 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>18</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3918,26 +3918,26 @@
         <v>125</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>90.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>154</v>
+        <v>125</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3951,26 +3951,26 @@
         <v>125</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>88.8</v>
+        <v>89.60000000000001</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Tativarru B.O</t>
+          <t>Vemanda B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3984,26 +3984,26 @@
         <v>125</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>88</v>
+        <v>88.8</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Tativarru B.O</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
@@ -4017,10 +4017,10 @@
         <v>125</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>85.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -4224,17 +4224,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
@@ -4248,26 +4248,26 @@
         <v>125</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>78.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -4281,26 +4281,26 @@
         <v>125</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>75.2</v>
+        <v>79.2</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4314,26 +4314,26 @@
         <v>125</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>72</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4347,26 +4347,26 @@
         <v>125</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>70.39999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4380,10 +4380,10 @@
         <v>125</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>61.6</v>
+        <v>70.39999999999999</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
@@ -4393,13 +4393,13 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>34</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4413,26 +4413,26 @@
         <v>125</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>60</v>
+        <v>68.8</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,26 +4446,26 @@
         <v>125</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>58.4</v>
+        <v>68.8</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,26 +4479,26 @@
         <v>125</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>65.60000000000001</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4512,26 +4512,26 @@
         <v>125</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>54.40000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>224</v>
+        <v>94</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>158</v>
+        <v>22</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,26 +4545,26 @@
         <v>125</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>52.8</v>
+        <v>57.59999999999999</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,26 +4578,26 @@
         <v>125</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>52.8</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -4611,26 +4611,26 @@
         <v>125</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>52.8</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4644,125 +4644,125 @@
         <v>125</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>51.2</v>
+        <v>52.8</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D34" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G34" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>52</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>94</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H34" s="15" t="n">
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H35" s="15" t="n">
         <v>51.2</v>
       </c>
-      <c r="I34" s="11" t="n">
+      <c r="I35" s="11" t="n">
         <v>61</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>Lakshminarasimhapuram B.O</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="n">
-        <v>71</v>
-      </c>
-      <c r="C35" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D35" s="18" t="n">
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Komaravolu B.O</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>148</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="D36" s="14" t="n">
+        <v>63</v>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="I36" s="11" t="n">
         <v>62</v>
-      </c>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G35" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H35" s="19" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Unikili B.O</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="n">
-        <v>67</v>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="E36" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G36" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H36" s="19" t="n">
-        <v>48</v>
-      </c>
-      <c r="I36" s="11" t="n">
-        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B37" s="17" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C37" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D37" s="18" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
@@ -4776,26 +4776,26 @@
         <v>125</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>47.2</v>
+        <v>49.6</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B38" s="17" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C38" s="17" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D38" s="18" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
@@ -4809,26 +4809,26 @@
         <v>125</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="C39" s="17" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -4842,26 +4842,26 @@
         <v>125</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>43.2</v>
+        <v>44</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
@@ -4875,23 +4875,23 @@
         <v>125</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>42.4</v>
+        <v>43.2</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D41" s="18" t="n">
         <v>53</v>
@@ -4917,17 +4917,17 @@
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -4941,26 +4941,26 @@
         <v>125</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>42.4</v>
+        <v>41.6</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>63</v>
+        <v>111</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -4974,26 +4974,26 @@
         <v>125</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>41.6</v>
+        <v>40.8</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -5007,10 +5007,10 @@
         <v>125</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>40.8</v>
+        <v>37.6</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45">
@@ -5082,17 +5082,17 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         <v>125</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>36.8</v>
+        <v>36</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48">
@@ -5214,17 +5214,17 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -5238,26 +5238,26 @@
         <v>125</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -5271,10 +5271,10 @@
         <v>125</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>33.6</v>
+        <v>34.4</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53">
@@ -5313,17 +5313,17 @@
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D54" s="18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
         <v>125</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>32</v>
+        <v>33.6</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
@@ -5412,17 +5412,17 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D57" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
@@ -5436,26 +5436,26 @@
         <v>125</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>27.2</v>
+        <v>31.2</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,26 +5469,26 @@
         <v>125</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>24.8</v>
+        <v>27.2</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5502,59 +5502,59 @@
         <v>125</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D60" s="18" t="n">
+        <v>30</v>
+      </c>
+      <c r="E60" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="H60" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F60" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G60" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H60" s="19" t="n">
-        <v>19.2</v>
-      </c>
       <c r="I60" s="11" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5568,23 +5568,23 @@
         <v>125</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>K.P.Agraharam B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>145</v>
+        <v>46</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="D62" s="18" t="n">
         <v>22</v>
@@ -5610,17 +5610,17 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>K.P.Agraharam B.O</t>
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="C63" s="17" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -5634,26 +5634,26 @@
         <v>125</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>16</v>
+        <v>17.6</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5667,26 +5667,26 @@
         <v>125</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>13.6</v>
+        <v>16</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5700,26 +5700,26 @@
         <v>125</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>12.8</v>
+        <v>13.6</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5733,23 +5733,23 @@
         <v>125</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>10.4</v>
+        <v>12.8</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D67" s="18" t="n">
         <v>13</v>
@@ -5944,13 +5944,13 @@
         </is>
       </c>
       <c r="B73" s="17" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C73" s="17" t="n">
         <v>121</v>
       </c>
       <c r="D73" s="18" t="n">
-        <v>-39</v>
+        <v>-29</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -5964,10 +5964,10 @@
         <v>125</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-31.2</v>
+        <v>-23.2</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -6084,13 +6084,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>48</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>250</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>127.6</v>
+        <v>128.4</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6150,13 +6150,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>34</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
         <v>250</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>106.8</v>
+        <v>107.2</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -6183,13 +6183,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>67</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>250</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>103.6</v>
+        <v>104.4</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>47</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         <v>250</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>95.19999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -6269,10 +6269,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>84.8</v>
+        <v>84.39999999999999</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
@@ -6480,13 +6480,13 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C15" s="17" t="n">
         <v>126</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6500,10 +6500,10 @@
         <v>250</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16">
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C16" s="17" t="n">
         <v>56</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>250</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1191</v>
+        <v>1204</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>771</v>
+        <v>777</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         <v>833.3333333333334</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>50.4</v>
+        <v>51.23999999999999</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>413.3333333333334</v>
+        <v>406.3333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -6829,10 +6829,10 @@
         <v>167</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>125</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>112</v>
+        <v>111.2</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C2" s="17" t="n">
         <v>121</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>-39</v>
+        <v>-29</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -6986,10 +6986,10 @@
         <v>125</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>-31.2</v>
+        <v>-23.2</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>48</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>250</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>127.6</v>
+        <v>128.4</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C2" s="17" t="n">
         <v>56</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>250</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3">
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="C3" s="17" t="n">
         <v>126</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         <v>250</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>21.6</v>
+        <v>25.6</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>12803</v>
+        <v>13001</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>4859</v>
+        <v>4885</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>7944</v>
+        <v>8116</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -623,13 +623,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>125</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -652,17 +652,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Vennanapudi B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>181</v>
+        <v>304</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>125</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>117.6</v>
+        <v>153.6</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -685,17 +685,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vennanapudi B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>125</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>116</v>
+        <v>117.6</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -718,17 +718,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -742,125 +742,125 @@
         <v>125</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>111.2</v>
+        <v>112.8</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Komatigunta Lock B.O</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>188</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>124</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>1</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Dosapadu B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Bokinala B.O</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>187</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>123</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>2</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Vemanda B.O</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Bollapadu B.O</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>147</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>122</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>3</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Bhushanagulla B.O</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -874,26 +874,26 @@
         <v>125</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>96.8</v>
+        <v>99.2</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -907,26 +907,26 @@
         <v>125</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>94.39999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -940,26 +940,26 @@
         <v>125</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>91.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -973,26 +973,26 @@
         <v>125</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>89.60000000000001</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         <v>125</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>88.8</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -1048,17 +1048,17 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -1072,10 +1072,10 @@
         <v>125</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>83.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -1085,13 +1085,13 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>23</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -1105,26 +1105,26 @@
         <v>125</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>82.39999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -1138,59 +1138,59 @@
         <v>125</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>82.39999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="C18" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="I18" s="11" t="n">
         <v>19</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>103</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>82.39999999999999</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -1204,89 +1204,89 @@
         <v>125</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>80.80000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>Garapadu B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>Putlacheruvu B.O</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B21" s="8" t="n">
         <v>137</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C21" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D21" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H20" s="10" t="n">
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="H21" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I21" s="11" t="n">
         <v>25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Valivarthipadu B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>138</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>39</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Velinuthala B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>99</v>
@@ -1312,17 +1312,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1336,26 +1336,26 @@
         <v>125</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>78.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1369,26 +1369,26 @@
         <v>125</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>71.2</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1402,26 +1402,26 @@
         <v>125</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>70.39999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>244</v>
+        <v>111</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>158</v>
+        <v>20</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1435,26 +1435,26 @@
         <v>125</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>68.8</v>
+        <v>72.8</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1468,26 +1468,26 @@
         <v>125</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>68.8</v>
+        <v>70.39999999999999</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1501,26 +1501,26 @@
         <v>125</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>65.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1534,26 +1534,26 @@
         <v>125</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>60.8</v>
+        <v>68.8</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1567,26 +1567,26 @@
         <v>125</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>57.59999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1600,26 +1600,26 @@
         <v>125</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -1633,26 +1633,26 @@
         <v>125</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>54.40000000000001</v>
+        <v>57.59999999999999</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         <v>125</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>52.8</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>7</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -1699,26 +1699,26 @@
         <v>125</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>52</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -1732,26 +1732,26 @@
         <v>125</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>51.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -1765,92 +1765,92 @@
         <v>125</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>50.4</v>
+        <v>52.8</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>Lakshminarasimhapuram B.O</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="n">
-        <v>71</v>
-      </c>
-      <c r="C37" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>62</v>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G37" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>49.6</v>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Addada B.O</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>52</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>Unikili B.O</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="n">
-        <v>67</v>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G38" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>48</v>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>51.2</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C39" s="17" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -1864,26 +1864,26 @@
         <v>125</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>44</v>
+        <v>49.6</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
@@ -1897,26 +1897,26 @@
         <v>125</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>43.2</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
@@ -1930,26 +1930,26 @@
         <v>125</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>42.4</v>
+        <v>44</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -1963,26 +1963,26 @@
         <v>125</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>41.6</v>
+        <v>44</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -1996,26 +1996,26 @@
         <v>125</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>40.8</v>
+        <v>42.4</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -2029,26 +2029,26 @@
         <v>125</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>37.6</v>
+        <v>41.6</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -2062,26 +2062,26 @@
         <v>125</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>37.6</v>
+        <v>40</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -2095,26 +2095,26 @@
         <v>125</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>37.6</v>
+        <v>39.2</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -2128,26 +2128,26 @@
         <v>125</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>36</v>
+        <v>38.4</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -2161,26 +2161,26 @@
         <v>125</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>36</v>
+        <v>37.6</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -2194,26 +2194,26 @@
         <v>125</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>35.2</v>
+        <v>37.6</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -2227,23 +2227,23 @@
         <v>125</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>35.2</v>
+        <v>36</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D51" s="18" t="n">
         <v>44</v>
@@ -2269,17 +2269,17 @@
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -2293,10 +2293,10 @@
         <v>125</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
@@ -2372,13 +2372,13 @@
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C55" s="17" t="n">
         <v>36</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -2392,23 +2392,23 @@
         <v>125</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>31.2</v>
+        <v>32.8</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D56" s="18" t="n">
         <v>39</v>
@@ -2434,14 +2434,14 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D57" s="18" t="n">
         <v>39</v>
@@ -2467,17 +2467,17 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         <v>125</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>27.2</v>
+        <v>31.2</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59">
@@ -2504,13 +2504,13 @@
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C59" s="17" t="n">
         <v>31</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         <v>125</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>24.8</v>
+        <v>28</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60">
@@ -2537,13 +2537,13 @@
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C60" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -2557,26 +2557,26 @@
         <v>125</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2590,26 +2590,26 @@
         <v>125</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>20.8</v>
+        <v>24</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         <v>125</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63">
@@ -2636,13 +2636,13 @@
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C63" s="17" t="n">
         <v>123</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -2656,26 +2656,26 @@
         <v>125</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>17.6</v>
+        <v>19.2</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -2689,26 +2689,26 @@
         <v>125</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2722,10 +2722,10 @@
         <v>125</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C66" s="17" t="n">
         <v>18</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2755,10 +2755,10 @@
         <v>125</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>12.8</v>
+        <v>14.4</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67">
@@ -2768,13 +2768,13 @@
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C67" s="17" t="n">
         <v>48</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -2788,10 +2788,10 @@
         <v>125</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>10.4</v>
+        <v>14.4</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68">
@@ -2837,10 +2837,10 @@
         <v>17</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -2854,10 +2854,10 @@
         <v>125</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70">
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -2953,10 +2953,10 @@
         <v>125</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-13.6</v>
+        <v>-5.600000000000001</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="B74" s="13" t="n">
-        <v>1204</v>
+        <v>1245</v>
       </c>
       <c r="C74" s="13" t="n">
-        <v>777</v>
+        <v>807</v>
       </c>
       <c r="D74" s="14" t="n">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
@@ -3019,10 +3019,10 @@
         <v>833.3333333333334</v>
       </c>
       <c r="H74" s="15" t="n">
-        <v>51.23999999999999</v>
+        <v>52.56</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>406.3333333333334</v>
+        <v>395.3333333333334</v>
       </c>
     </row>
     <row r="75">
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>250</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>149.2</v>
+        <v>149.6</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3065,13 +3065,13 @@
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
         <v>250</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>128.4</v>
+        <v>133.2</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
@@ -3098,13 +3098,13 @@
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>67</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         <v>250</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>250</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>104.4</v>
+        <v>105.2</v>
       </c>
       <c r="I79" s="6" t="n">
         <v>0</v>
@@ -3200,10 +3200,10 @@
         <v>289</v>
       </c>
       <c r="C80" s="8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         <v>250</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>96.8</v>
+        <v>96</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81">
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="B81" s="8" t="n">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="C81" s="8" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
@@ -3250,10 +3250,10 @@
         <v>250</v>
       </c>
       <c r="H81" s="10" t="n">
-        <v>84.39999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="B83" s="13" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C83" s="13" t="n">
         <v>49</v>
       </c>
       <c r="D83" s="14" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         <v>250</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>62.8</v>
+        <v>63.6</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="84">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D84" s="14" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
@@ -3349,10 +3349,10 @@
         <v>250</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>58.8</v>
+        <v>59.2</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="85">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C86" s="17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3415,10 +3415,10 @@
         <v>250</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>45.6</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="87">
@@ -3428,10 +3428,10 @@
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C87" s="17" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D87" s="18" t="n">
         <v>108</v>
@@ -3461,13 +3461,13 @@
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="C88" s="17" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3481,10 +3481,10 @@
         <v>250</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>25.6</v>
+        <v>39.2</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="89">
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C89" s="17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3514,10 +3514,10 @@
         <v>250</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>21.6</v>
+        <v>24.8</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -3601,13 +3601,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>125</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -3630,17 +3630,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Vennanapudi B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>181</v>
+        <v>304</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>125</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>117.6</v>
+        <v>153.6</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -3663,17 +3663,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vennanapudi B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>125</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>116</v>
+        <v>117.6</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -3696,17 +3696,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -3720,125 +3720,125 @@
         <v>125</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>111.2</v>
+        <v>112.8</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Komatigunta Lock B.O</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>188</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>124</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>99.2</v>
-      </c>
-      <c r="I6" s="11" t="n">
-        <v>1</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Dosapadu B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>167</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Bokinala B.O</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>187</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>64</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>123</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>2</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Vemanda B.O</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>133</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Bollapadu B.O</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>147</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>122</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>97.59999999999999</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>3</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Bhushanagulla B.O</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Vinnakota B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3852,26 +3852,26 @@
         <v>125</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>96.8</v>
+        <v>99.2</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Nandamuru B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -3885,26 +3885,26 @@
         <v>125</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>94.39999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Pedapalaparru B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3918,26 +3918,26 @@
         <v>125</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>91.2</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Bhushanagulla B.O</t>
+          <t>Pedapalaparru B.O</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
@@ -3951,26 +3951,26 @@
         <v>125</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>89.60000000000001</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Vemanda B.O</t>
+          <t>Chowtapalli B.O</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
@@ -3984,10 +3984,10 @@
         <v>125</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>88.8</v>
+        <v>92.80000000000001</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -4026,17 +4026,17 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Nandamuru B.O</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>125</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>83.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -4063,13 +4063,13 @@
         </is>
       </c>
       <c r="B16" s="8" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>23</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
@@ -4083,26 +4083,26 @@
         <v>125</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>82.39999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Kanukollu B.O</t>
+          <t>Moparru B.O</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
@@ -4116,59 +4116,59 @@
         <v>125</v>
       </c>
       <c r="H17" s="10" t="n">
-        <v>82.39999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I17" s="11" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Moparru B.O</t>
+          <t>Kanukollu B.O</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="C18" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="I18" s="11" t="n">
         <v>19</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>103</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>82.39999999999999</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Garapadu B.O</t>
+          <t>Guruvindagunta B.O</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
@@ -4182,76 +4182,76 @@
         <v>125</v>
       </c>
       <c r="H19" s="10" t="n">
-        <v>80.80000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>Garapadu B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>112</v>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>Putlacheruvu B.O</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B21" s="8" t="n">
         <v>137</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C21" s="8" t="n">
         <v>37</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D21" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H20" s="10" t="n">
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>125</v>
+      </c>
+      <c r="H21" s="10" t="n">
         <v>80</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I21" s="11" t="n">
         <v>25</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Velinuthala B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>152</v>
-      </c>
-      <c r="C21" s="13" t="n">
-        <v>53</v>
-      </c>
-      <c r="D21" s="14" t="n">
-        <v>99</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="I21" s="11" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="22">
@@ -4290,17 +4290,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Velinuthala B.O</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>104</v>
+        <v>152</v>
       </c>
       <c r="C23" s="13" t="n">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4314,26 +4314,26 @@
         <v>125</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>78.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Guruvindagunta B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4347,26 +4347,26 @@
         <v>125</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>71.2</v>
+        <v>77.60000000000001</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4380,59 +4380,59 @@
         <v>125</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>70.39999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C26" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>91</v>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="I26" s="11" t="n">
         <v>34</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>86</v>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G26" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="I26" s="11" t="n">
-        <v>39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>244</v>
+        <v>111</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4446,26 +4446,26 @@
         <v>125</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>68.8</v>
+        <v>70.39999999999999</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4479,26 +4479,26 @@
         <v>125</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>65.60000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Chowtapalli B.O</t>
+          <t>Tenneru B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>131</v>
+        <v>245</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>55</v>
+        <v>159</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4512,26 +4512,26 @@
         <v>125</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>60.8</v>
+        <v>68.8</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Ponukumadu B.O</t>
+          <t>Unikili B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4545,26 +4545,26 @@
         <v>125</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>57.59999999999999</v>
+        <v>58.4</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Gandhi Asramam B.O</t>
+          <t>Komaravolu B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>77</v>
+        <v>158</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4578,26 +4578,26 @@
         <v>125</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>56.00000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Nandivada B.O</t>
+          <t>Ponukumadu B.O</t>
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
@@ -4611,26 +4611,26 @@
         <v>125</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>54.40000000000001</v>
+        <v>57.59999999999999</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Guntakoduru B.O</t>
+          <t>Pedavirivada B.O</t>
         </is>
       </c>
       <c r="B33" s="13" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C33" s="13" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
@@ -4644,26 +4644,26 @@
         <v>125</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>52.8</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I33" s="11" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Pedavirivada B.O</t>
+          <t>Gandhi Asramam B.O</t>
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C34" s="13" t="n">
         <v>7</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
@@ -4677,26 +4677,26 @@
         <v>125</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>52</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Pedakamanapudi B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C35" s="13" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
@@ -4710,26 +4710,26 @@
         <v>125</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>51.2</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="I35" s="11" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Guntakoduru B.O</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="C36" s="13" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
@@ -4743,92 +4743,92 @@
         <v>125</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>50.4</v>
+        <v>52.8</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>Lakshminarasimhapuram B.O</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="n">
-        <v>71</v>
-      </c>
-      <c r="C37" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="D37" s="18" t="n">
-        <v>62</v>
-      </c>
-      <c r="E37" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G37" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H37" s="19" t="n">
-        <v>49.6</v>
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Addada B.O</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>34</v>
+      </c>
+      <c r="D37" s="14" t="n">
+        <v>65</v>
+      </c>
+      <c r="E37" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>52</v>
       </c>
       <c r="I37" s="11" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>Unikili B.O</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="n">
-        <v>67</v>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="D38" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="E38" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G38" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H38" s="19" t="n">
-        <v>48</v>
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Pedakamanapudi B.O</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>31</v>
+      </c>
+      <c r="D38" s="14" t="n">
+        <v>64</v>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>51.2</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C39" s="17" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -4842,26 +4842,26 @@
         <v>125</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>44</v>
+        <v>49.6</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Siddantham B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="C40" s="17" t="n">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="D40" s="18" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
@@ -4875,26 +4875,26 @@
         <v>125</v>
       </c>
       <c r="H40" s="19" t="n">
-        <v>43.2</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
@@ -4908,26 +4908,26 @@
         <v>125</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>42.4</v>
+        <v>44</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -4941,26 +4941,26 @@
         <v>125</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>41.6</v>
+        <v>44</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -4974,26 +4974,26 @@
         <v>125</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>40.8</v>
+        <v>42.4</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Ramapuram B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -5007,26 +5007,26 @@
         <v>125</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>37.6</v>
+        <v>41.6</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="C45" s="17" t="n">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -5040,26 +5040,26 @@
         <v>125</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>37.6</v>
+        <v>40</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -5073,26 +5073,26 @@
         <v>125</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>37.6</v>
+        <v>39.2</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Ramapuram B.O</t>
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C47" s="17" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -5106,59 +5106,59 @@
         <v>125</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>36</v>
+        <v>38.4</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Addada B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D48" s="18" t="n">
+        <v>47</v>
+      </c>
+      <c r="E48" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>125</v>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="I48" s="11" t="n">
         <v>78</v>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="D48" s="18" t="n">
-        <v>45</v>
-      </c>
-      <c r="E48" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F48" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G48" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H48" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="I48" s="11" t="n">
-        <v>80</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Siddantham B.O</t>
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="C49" s="17" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -5172,26 +5172,26 @@
         <v>125</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>35.2</v>
+        <v>37.6</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -5205,23 +5205,23 @@
         <v>125</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>35.2</v>
+        <v>36</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D51" s="18" t="n">
         <v>44</v>
@@ -5251,13 +5251,13 @@
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D52" s="18" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
@@ -5271,10 +5271,10 @@
         <v>125</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>34.4</v>
+        <v>35.2</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
@@ -5350,13 +5350,13 @@
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C55" s="17" t="n">
         <v>36</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -5370,10 +5370,10 @@
         <v>125</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>31.2</v>
+        <v>32.8</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56">
@@ -5445,17 +5445,17 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="D58" s="18" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -5469,10 +5469,10 @@
         <v>125</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>27.2</v>
+        <v>31.2</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59">
@@ -5482,13 +5482,13 @@
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C59" s="17" t="n">
         <v>31</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5502,10 +5502,10 @@
         <v>125</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>24.8</v>
+        <v>28</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60">
@@ -5515,13 +5515,13 @@
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C60" s="17" t="n">
         <v>13</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -5535,26 +5535,26 @@
         <v>125</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Sankarshanapuram B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5568,26 +5568,26 @@
         <v>125</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>20.8</v>
+        <v>24</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>Dandiganapudi B.O</t>
+          <t>Sankarshanapuram B.O</t>
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="C62" s="17" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -5601,10 +5601,10 @@
         <v>125</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>17.6</v>
+        <v>20.8</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="63">
@@ -5614,13 +5614,13 @@
         </is>
       </c>
       <c r="B63" s="17" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C63" s="17" t="n">
         <v>123</v>
       </c>
       <c r="D63" s="18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
@@ -5634,26 +5634,26 @@
         <v>125</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>17.6</v>
+        <v>19.2</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Dandiganapudi B.O</t>
         </is>
       </c>
       <c r="B64" s="17" t="n">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="C64" s="17" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="D64" s="18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5667,26 +5667,26 @@
         <v>125</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5700,27 +5700,27 @@
         <v>125</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="C66" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="D66" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="D66" s="18" t="n">
-        <v>16</v>
-      </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
           <t>BO</t>
@@ -5733,26 +5733,26 @@
         <v>125</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>12.8</v>
+        <v>14.4</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D67" s="18" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5766,10 +5766,10 @@
         <v>125</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>10.4</v>
+        <v>14.4</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68">
@@ -5815,10 +5815,10 @@
         <v>17</v>
       </c>
       <c r="C69" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D69" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5832,10 +5832,10 @@
         <v>125</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="70">
@@ -5911,13 +5911,13 @@
         </is>
       </c>
       <c r="B72" s="17" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -5931,10 +5931,10 @@
         <v>125</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-13.6</v>
+        <v>-5.600000000000001</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73">
@@ -6051,13 +6051,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6071,7 +6071,7 @@
         <v>250</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>149.2</v>
+        <v>149.6</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6084,13 +6084,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>250</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>128.4</v>
+        <v>133.2</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6117,13 +6117,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>67</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>250</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6183,13 +6183,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>250</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>104.4</v>
+        <v>105.2</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>289</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
@@ -6236,10 +6236,10 @@
         <v>250</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>96.8</v>
+        <v>96</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -6269,10 +6269,10 @@
         <v>250</v>
       </c>
       <c r="H8" s="10" t="n">
-        <v>84.39999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -6315,13 +6315,13 @@
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>49</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
@@ -6335,10 +6335,10 @@
         <v>250</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>62.8</v>
+        <v>63.6</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -6348,13 +6348,13 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
@@ -6368,10 +6368,10 @@
         <v>250</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>58.8</v>
+        <v>59.2</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -6414,13 +6414,13 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6434,10 +6434,10 @@
         <v>250</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>45.6</v>
+        <v>46.40000000000001</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D14" s="18" t="n">
         <v>108</v>
@@ -6480,13 +6480,13 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6500,10 +6500,10 @@
         <v>250</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>25.6</v>
+        <v>39.2</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6533,10 +6533,10 @@
         <v>250</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>21.6</v>
+        <v>24.8</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B2" s="13" t="n">
-        <v>1204</v>
+        <v>1245</v>
       </c>
       <c r="C2" s="13" t="n">
-        <v>777</v>
+        <v>807</v>
       </c>
       <c r="D2" s="14" t="n">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         <v>833.3333333333334</v>
       </c>
       <c r="H2" s="15" t="n">
-        <v>51.23999999999999</v>
+        <v>52.56</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>406.3333333333334</v>
+        <v>395.3333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -6727,13 +6727,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>125</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6756,17 +6756,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Koyyagurapadu B.O</t>
+          <t>Vennanapudi B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>181</v>
+        <v>304</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>147</v>
+        <v>192</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>125</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>117.6</v>
+        <v>153.6</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6789,17 +6789,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Vennanapudi B.O</t>
+          <t>Koyyagurapadu B.O</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>112</v>
+        <v>34</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>125</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>116</v>
+        <v>117.6</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -6822,17 +6822,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Vinnakota B.O</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         <v>125</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>111.2</v>
+        <v>112.8</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
@@ -6855,17 +6855,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Dosapadu B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6879,10 +6879,10 @@
         <v>125</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>99.2</v>
+        <v>111.2</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6999,13 +6999,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7019,10 +7019,10 @@
         <v>125</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>-13.6</v>
+        <v>-5.600000000000001</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
@@ -7101,10 +7101,10 @@
         <v>17</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -7118,10 +7118,10 @@
         <v>125</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>250</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>149.2</v>
+        <v>149.6</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7238,13 +7238,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>250</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>128.4</v>
+        <v>133.2</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7271,13 +7271,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>67</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>250</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C2" s="17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>250</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>21.6</v>
+        <v>24.8</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3">
@@ -7411,13 +7411,13 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         <v>250</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>25.6</v>
+        <v>39.2</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>108</v>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>13001</v>
+        <v>13521</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>4885</v>
+        <v>5020</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>8116</v>
+        <v>8501</v>
       </c>
     </row>
   </sheetData>

--- a/Gudivada_Net_Accounts_Latest.xlsx
+++ b/Gudivada_Net_Accounts_Latest.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="All Offices" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="BO Performance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SO Performance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HO Performance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Top 5 BOs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Bottom 5 BOs" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Top 3 SOs" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Bottom 3 SOs" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Summary" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Offices" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BO Performance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO Performance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HO Performance" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 5 BOs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bottom 5 BOs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 3 SOs" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bottom 3 SOs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Offices'!$A$1:$I$89</definedName>
@@ -619,17 +619,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Vennanapudi B.O</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -640,10 +640,10 @@
         <v>300</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>156</v>
+        <v>131.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -652,17 +652,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Vennanapudi B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -673,194 +673,194 @@
         <v>300</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>153.6</v>
+        <v>130</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Koyyagurapadu B.O</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="8" t="n">
+        <v>182</v>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>117.6</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0</v>
+      <c r="D4" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>98.66666666666667</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Vinnakota B.O</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="8" t="n">
         <v>161</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="9" t="n">
         <v>141</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0</v>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Bhushanagulla B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>154</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Dosapadu B.O</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="B7" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>139</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>92.66666666666666</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Vemanda B.O</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B8" s="8" t="n">
         <v>176</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C8" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D8" s="9" t="n">
         <v>133</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>106.4</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Bhushanagulla B.O</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>88.66666666666667</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>64</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -871,29 +871,29 @@
         <v>300</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>99.2</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -904,29 +904,29 @@
         <v>300</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>98.40000000000001</v>
+        <v>81.33333333333333</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -937,359 +937,359 @@
         <v>300</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>97.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Pedapalaparru B.O</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>134</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Chowtapalli B.O</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B13" s="13" t="n">
         <v>171</v>
       </c>
-      <c r="C12" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>116</v>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>92.80000000000001</v>
-      </c>
-      <c r="I12" s="11" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Pedapalaparru B.O</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>134</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>116</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>92.80000000000001</v>
+      <c r="C13" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>76.66666666666667</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Guruvindagunta B.O</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>126</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Tativarru B.O</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B15" s="13" t="n">
         <v>127</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C15" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D15" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Nandamuru B.O</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B16" s="13" t="n">
         <v>198</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C16" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D16" s="14" t="n">
         <v>108</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Gunnanapudi B.O</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B17" s="13" t="n">
         <v>130</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C17" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D17" s="14" t="n">
         <v>107</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>71.33333333333334</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Moparru B.O</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B18" s="13" t="n">
         <v>126</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C18" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D18" s="14" t="n">
         <v>107</v>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>71.33333333333334</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>Kanukollu B.O</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B19" s="13" t="n">
         <v>155</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C19" s="13" t="n">
         <v>49</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D19" s="14" t="n">
         <v>106</v>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Guruvindagunta B.O</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>104</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>83.2</v>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>70.66666666666667</v>
       </c>
       <c r="I19" s="11" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Garapadu B.O</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="13" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="8" t="n">
+      <c r="C20" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="14" t="n">
         <v>102</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>81.59999999999999</v>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>68</v>
       </c>
       <c r="I20" s="11" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Putlacheruvu B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>137</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="D21" s="9" t="n">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Gandhi Asramam B.O</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>107</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>80</v>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>66.66666666666666</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -1300,13 +1300,13 @@
         <v>300</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>79.2</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -1316,13 +1316,13 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>53</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -1333,13 +1333,13 @@
         <v>300</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>79.2</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C24" s="13" t="n">
         <v>57</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -1366,29 +1366,29 @@
         <v>300</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>77.60000000000001</v>
+        <v>66</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -1399,29 +1399,29 @@
         <v>300</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>74.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -1432,29 +1432,29 @@
         <v>300</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>72.8</v>
+        <v>62</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
         <v>111</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -1465,29 +1465,29 @@
         <v>300</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>70.39999999999999</v>
+        <v>60.66666666666667</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -1498,29 +1498,29 @@
         <v>300</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>69.59999999999999</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>245</v>
+        <v>121</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>159</v>
+        <v>34</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -1531,29 +1531,29 @@
         <v>300</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>68.8</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>158</v>
+        <v>99</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -1564,29 +1564,29 @@
         <v>300</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>58.4</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>90</v>
+        <v>124</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -1597,260 +1597,260 @@
         <v>300</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>58.4</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
+          <t>Tenneru B.O</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>246</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>171</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Komaravolu B.O</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>158</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>48.66666666666667</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>48.66666666666667</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
           <t>Ponukumadu B.O</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
+      <c r="B35" s="17" t="n">
         <v>94</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C35" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D35" s="18" t="n">
         <v>72</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>57.59999999999999</v>
-      </c>
-      <c r="I32" s="11" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Gandhi Asramam B.O</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="n">
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Pedavirivada B.O</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
         <v>77</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C36" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D36" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Pedavirivada B.O</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n">
-        <v>77</v>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Nandivada B.O</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="n">
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Guntakoduru B.O</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>83</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="I37" s="11" t="n">
         <v>84</v>
       </c>
-      <c r="C35" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>68</v>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>54.40000000000001</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Guntakoduru B.O</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n">
-        <v>83</v>
-      </c>
-      <c r="C36" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>66</v>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="I36" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Addada B.O</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n">
+      <c r="B38" s="17" t="n">
         <v>99</v>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C38" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D38" s="18" t="n">
         <v>65</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>52</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>Pedakamanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n">
-        <v>95</v>
-      </c>
-      <c r="C38" s="13" t="n">
-        <v>31</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>64</v>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>51.2</v>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>43.33333333333334</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Pedakamanapudi B.O</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C39" s="17" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -1861,62 +1861,62 @@
         <v>300</v>
       </c>
       <c r="G39" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>49.6</v>
+        <v>42.66666666666667</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="I40" s="11" t="n">
         <v>87</v>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>58</v>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G40" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>46.40000000000001</v>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
@@ -1927,29 +1927,29 @@
         <v>300</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>44</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -1960,29 +1960,29 @@
         <v>300</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>44</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -1993,29 +1993,29 @@
         <v>300</v>
       </c>
       <c r="G43" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>42.4</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -2026,29 +2026,29 @@
         <v>300</v>
       </c>
       <c r="G44" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>41.6</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C45" s="17" t="n">
         <v>36</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -2059,29 +2059,29 @@
         <v>300</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>40</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -2092,13 +2092,13 @@
         <v>300</v>
       </c>
       <c r="G46" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>39.2</v>
+        <v>34.66666666666667</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47">
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C47" s="17" t="n">
         <v>17</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -2125,29 +2125,29 @@
         <v>300</v>
       </c>
       <c r="G47" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>38.4</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>300</v>
       </c>
       <c r="G48" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>37.6</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49">
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C49" s="17" t="n">
         <v>85</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -2191,29 +2191,29 @@
         <v>300</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>37.6</v>
+        <v>32</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -2224,29 +2224,29 @@
         <v>300</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>36</v>
+        <v>30.66666666666666</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -2257,26 +2257,26 @@
         <v>300</v>
       </c>
       <c r="G51" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>35.2</v>
+        <v>30</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D52" s="18" t="n">
         <v>44</v>
@@ -2290,29 +2290,29 @@
         <v>300</v>
       </c>
       <c r="G52" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>35.2</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -2323,26 +2323,26 @@
         <v>300</v>
       </c>
       <c r="G53" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>33.6</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D54" s="18" t="n">
         <v>42</v>
@@ -2356,29 +2356,29 @@
         <v>300</v>
       </c>
       <c r="G54" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>33.6</v>
+        <v>28</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>83</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -2389,29 +2389,29 @@
         <v>300</v>
       </c>
       <c r="G55" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>32.8</v>
+        <v>28</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -2422,26 +2422,26 @@
         <v>300</v>
       </c>
       <c r="G56" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>31.2</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D57" s="18" t="n">
         <v>39</v>
@@ -2455,26 +2455,26 @@
         <v>300</v>
       </c>
       <c r="G57" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>31.2</v>
+        <v>26</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D58" s="18" t="n">
         <v>39</v>
@@ -2488,29 +2488,29 @@
         <v>300</v>
       </c>
       <c r="G58" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>31.2</v>
+        <v>26</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -2521,29 +2521,29 @@
         <v>300</v>
       </c>
       <c r="G59" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -2554,29 +2554,29 @@
         <v>300</v>
       </c>
       <c r="G60" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>24.8</v>
+        <v>22</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -2587,13 +2587,13 @@
         <v>300</v>
       </c>
       <c r="G61" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>24</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62">
@@ -2603,13 +2603,13 @@
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C62" s="17" t="n">
         <v>5</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -2620,13 +2620,13 @@
         <v>300</v>
       </c>
       <c r="G62" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>20.8</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>99</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63">
@@ -2653,13 +2653,13 @@
         <v>300</v>
       </c>
       <c r="G63" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64">
@@ -2686,29 +2686,29 @@
         <v>300</v>
       </c>
       <c r="G64" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>18.4</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -2719,29 +2719,29 @@
         <v>300</v>
       </c>
       <c r="G65" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>15.2</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Billapadu</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>36</v>
+        <v>116</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>18</v>
+        <v>97</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -2752,26 +2752,26 @@
         <v>300</v>
       </c>
       <c r="G66" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>14.4</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>107</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Billapadu</t>
         </is>
       </c>
       <c r="B67" s="17" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="C67" s="17" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="D67" s="18" t="n">
         <v>18</v>
@@ -2785,13 +2785,13 @@
         <v>300</v>
       </c>
       <c r="G67" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>14.4</v>
+        <v>12</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C68" s="17" t="n">
         <v>36</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -2818,13 +2818,13 @@
         <v>300</v>
       </c>
       <c r="G68" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>7.199999999999999</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69">
@@ -2851,13 +2851,13 @@
         <v>300</v>
       </c>
       <c r="G69" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70">
@@ -2884,13 +2884,13 @@
         <v>300</v>
       </c>
       <c r="G70" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>-0.8</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71">
@@ -2917,13 +2917,13 @@
         <v>300</v>
       </c>
       <c r="G71" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>-4.8</v>
+        <v>-4</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72">
@@ -2936,10 +2936,10 @@
         <v>250</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -2950,13 +2950,13 @@
         <v>300</v>
       </c>
       <c r="G72" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-5.600000000000001</v>
+        <v>-5.333333333333334</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73">
@@ -2983,46 +2983,46 @@
         <v>300</v>
       </c>
       <c r="G73" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-23.2</v>
+        <v>-19.33333333333333</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="A74" s="16" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B74" s="13" t="n">
-        <v>1245</v>
-      </c>
-      <c r="C74" s="13" t="n">
-        <v>807</v>
-      </c>
-      <c r="D74" s="14" t="n">
-        <v>438</v>
-      </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="B74" s="17" t="n">
+        <v>1255</v>
+      </c>
+      <c r="C74" s="17" t="n">
+        <v>810</v>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>445</v>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F74" s="13" t="n">
+      <c r="F74" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="G74" s="13" t="n">
-        <v>833.3333333333334</v>
-      </c>
-      <c r="H74" s="15" t="n">
-        <v>52.56</v>
+      <c r="G74" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H74" s="19" t="n">
+        <v>44.5</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>395.3333333333334</v>
+        <v>555</v>
       </c>
     </row>
     <row r="75">
@@ -3032,13 +3032,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3049,10 +3049,10 @@
         <v>600</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>149.6</v>
+        <v>124</v>
       </c>
       <c r="I75" s="6" t="n">
         <v>0</v>
@@ -3082,10 +3082,10 @@
         <v>600</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>133.2</v>
+        <v>111</v>
       </c>
       <c r="I76" s="6" t="n">
         <v>0</v>
@@ -3115,79 +3115,79 @@
         <v>600</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>124</v>
+        <v>103.3333333333333</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>Rudrapaka S.O</t>
         </is>
       </c>
-      <c r="B78" s="3" t="n">
+      <c r="B78" s="8" t="n">
         <v>302</v>
       </c>
-      <c r="C78" s="3" t="n">
+      <c r="C78" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="D78" s="4" t="n">
+      <c r="D78" s="9" t="n">
         <v>268</v>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F78" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G78" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>107.2</v>
-      </c>
-      <c r="I78" s="6" t="n">
-        <v>0</v>
+      <c r="G78" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="H78" s="10" t="n">
+        <v>89.33333333333333</v>
+      </c>
+      <c r="I78" s="11" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>Mudunuru S.O</t>
         </is>
       </c>
-      <c r="B79" s="3" t="n">
+      <c r="B79" s="8" t="n">
         <v>335</v>
       </c>
-      <c r="C79" s="3" t="n">
+      <c r="C79" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="D79" s="4" t="n">
+      <c r="D79" s="9" t="n">
         <v>263</v>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F79" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G79" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>105.2</v>
-      </c>
-      <c r="I79" s="6" t="n">
-        <v>0</v>
+      <c r="G79" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="H79" s="10" t="n">
+        <v>87.66666666666667</v>
+      </c>
+      <c r="I79" s="11" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="80">
@@ -3214,46 +3214,46 @@
         <v>600</v>
       </c>
       <c r="G80" s="8" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H80" s="10" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="inlineStr">
+      <c r="A81" s="12" t="inlineStr">
         <is>
           <t>Mudinepalli S.O</t>
         </is>
       </c>
-      <c r="B81" s="8" t="n">
-        <v>486</v>
-      </c>
-      <c r="C81" s="8" t="n">
-        <v>258</v>
-      </c>
-      <c r="D81" s="9" t="n">
-        <v>228</v>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="B81" s="13" t="n">
+        <v>490</v>
+      </c>
+      <c r="C81" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>230</v>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n">
+      <c r="F81" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G81" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="H81" s="10" t="n">
-        <v>91.2</v>
+      <c r="G81" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="H81" s="15" t="n">
+        <v>76.66666666666667</v>
       </c>
       <c r="I81" s="11" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="82">
@@ -3266,10 +3266,10 @@
         <v>223</v>
       </c>
       <c r="C82" s="13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D82" s="14" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
@@ -3280,13 +3280,13 @@
         <v>600</v>
       </c>
       <c r="G82" s="13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>78.8</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>53</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83">
@@ -3313,95 +3313,95 @@
         <v>600</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>63.6</v>
+        <v>53</v>
       </c>
       <c r="I83" s="11" t="n">
-        <v>91</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="12" t="inlineStr">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>Indupalli S.O</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="n">
+        <v>275</v>
+      </c>
+      <c r="C84" s="17" t="n">
+        <v>127</v>
+      </c>
+      <c r="D84" s="18" t="n">
+        <v>148</v>
+      </c>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="G84" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="H84" s="19" t="n">
+        <v>49.33333333333334</v>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="inlineStr">
         <is>
           <t>Rajendranagar Colony S.O</t>
         </is>
       </c>
-      <c r="B84" s="13" t="n">
-        <v>353</v>
-      </c>
-      <c r="C84" s="13" t="n">
-        <v>205</v>
-      </c>
-      <c r="D84" s="14" t="n">
-        <v>148</v>
-      </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="B85" s="17" t="n">
+        <v>354</v>
+      </c>
+      <c r="C85" s="17" t="n">
+        <v>212</v>
+      </c>
+      <c r="D85" s="18" t="n">
+        <v>142</v>
+      </c>
+      <c r="E85" s="16" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F84" s="13" t="n">
+      <c r="F85" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="G84" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="H84" s="15" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="I84" s="11" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>Golvepalli (Zami) S.O</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="n">
-        <v>143</v>
-      </c>
-      <c r="C85" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D85" s="14" t="n">
-        <v>130</v>
-      </c>
-      <c r="E85" s="12" t="inlineStr">
-        <is>
-          <t>SO</t>
-        </is>
-      </c>
-      <c r="F85" s="13" t="n">
-        <v>600</v>
-      </c>
-      <c r="G85" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="H85" s="15" t="n">
-        <v>52</v>
+      <c r="G85" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="H85" s="19" t="n">
+        <v>47.33333333333334</v>
       </c>
       <c r="I85" s="11" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>Tamirisa S.O</t>
+          <t>Golvepalli (Zami) S.O</t>
         </is>
       </c>
       <c r="B86" s="17" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C86" s="17" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="D86" s="18" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
@@ -3412,29 +3412,29 @@
         <v>600</v>
       </c>
       <c r="G86" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H86" s="19" t="n">
-        <v>46.40000000000001</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I86" s="11" t="n">
-        <v>134</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>Janardhanapuram S.O</t>
+          <t>Tamirisa S.O</t>
         </is>
       </c>
       <c r="B87" s="17" t="n">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="C87" s="17" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D87" s="18" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E87" s="16" t="inlineStr">
         <is>
@@ -3445,29 +3445,29 @@
         <v>600</v>
       </c>
       <c r="G87" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H87" s="19" t="n">
-        <v>43.2</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I87" s="11" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>Indupalli S.O</t>
+          <t>Janardhanapuram S.O</t>
         </is>
       </c>
       <c r="B88" s="17" t="n">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="C88" s="17" t="n">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="D88" s="18" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
@@ -3478,13 +3478,13 @@
         <v>600</v>
       </c>
       <c r="G88" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H88" s="19" t="n">
-        <v>39.2</v>
+        <v>37</v>
       </c>
       <c r="I88" s="11" t="n">
-        <v>152</v>
+        <v>189</v>
       </c>
     </row>
     <row r="89">
@@ -3494,13 +3494,13 @@
         </is>
       </c>
       <c r="B89" s="17" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C89" s="17" t="n">
         <v>57</v>
       </c>
       <c r="D89" s="18" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E89" s="16" t="inlineStr">
         <is>
@@ -3511,13 +3511,13 @@
         <v>600</v>
       </c>
       <c r="G89" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>24.8</v>
+        <v>21</v>
       </c>
       <c r="I89" s="11" t="n">
-        <v>188</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3597,17 +3597,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Vennanapudi B.O</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -3618,10 +3618,10 @@
         <v>300</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>156</v>
+        <v>131.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -3630,17 +3630,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Vennanapudi B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -3651,194 +3651,194 @@
         <v>300</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>153.6</v>
+        <v>130</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Koyyagurapadu B.O</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>181</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B4" s="8" t="n">
+        <v>182</v>
+      </c>
+      <c r="C4" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>147</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>117.6</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0</v>
+      <c r="D4" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>98.66666666666667</v>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Vinnakota B.O</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="8" t="n">
         <v>161</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="9" t="n">
         <v>141</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>112.8</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0</v>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>94</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Bhushanagulla B.O</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n">
+        <v>154</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Dosapadu B.O</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
-        <v>167</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="B7" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="D7" s="9" t="n">
         <v>139</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>92.66666666666666</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Vemanda B.O</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B8" s="8" t="n">
         <v>176</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C8" s="8" t="n">
         <v>43</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D8" s="9" t="n">
         <v>133</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>106.4</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Bhushanagulla B.O</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>146</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>300</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0</v>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>150</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>88.66666666666667</v>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Komatigunta Lock B.O</t>
+          <t>Bokinala B.O</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>64</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
@@ -3849,29 +3849,29 @@
         <v>300</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>99.2</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Bokinala B.O</t>
+          <t>Bollapadu B.O</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>187</v>
+        <v>147</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
@@ -3882,29 +3882,29 @@
         <v>300</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H10" s="10" t="n">
-        <v>98.40000000000001</v>
+        <v>81.33333333333333</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Bollapadu B.O</t>
+          <t>Komatigunta Lock B.O</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
@@ -3915,359 +3915,359 @@
         <v>300</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>97.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="I11" s="11" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Pedapalaparru B.O</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B12" s="13" t="n">
         <v>134</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="14" t="n">
         <v>116</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G12" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>92.80000000000001</v>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>77.33333333333333</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Chowtapalli B.O</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B13" s="13" t="n">
         <v>171</v>
       </c>
-      <c r="C13" s="8" t="n">
-        <v>55</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>116</v>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>92.80000000000001</v>
+      <c r="C13" s="13" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>76.66666666666667</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Guruvindagunta B.O</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>126</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>76</v>
+      </c>
+      <c r="I14" s="11" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Tativarru B.O</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B15" s="13" t="n">
         <v>127</v>
       </c>
-      <c r="C14" s="8" t="n">
+      <c r="C15" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D15" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>88</v>
-      </c>
-      <c r="I14" s="11" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Nandamuru B.O</t>
         </is>
       </c>
-      <c r="B15" s="8" t="n">
+      <c r="B16" s="13" t="n">
         <v>198</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C16" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D16" s="14" t="n">
         <v>108</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H15" s="10" t="n">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="I16" s="11" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Moparru B.O</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>126</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>19</v>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>107</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>71.33333333333334</v>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Gunnanapudi B.O</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B18" s="13" t="n">
         <v>130</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C18" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D18" s="14" t="n">
         <v>107</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="I16" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Moparru B.O</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
-        <v>126</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="D17" s="9" t="n">
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>71.33333333333334</v>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Kanukollu B.O</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>155</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>106</v>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Garapadu B.O</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>112</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>102</v>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Gandhi Asramam B.O</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
         <v>107</v>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>85.59999999999999</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Kanukollu B.O</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="n">
-        <v>155</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>49</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>106</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="I18" s="11" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Guruvindagunta B.O</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n">
-        <v>116</v>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>104</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F19" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G19" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Garapadu B.O</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
-        <v>112</v>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>102</v>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>81.59999999999999</v>
-      </c>
-      <c r="I20" s="11" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Putlacheruvu B.O</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>137</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>37</v>
-      </c>
-      <c r="D21" s="9" t="n">
+      <c r="C21" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" s="14" t="n">
         <v>100</v>
       </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>125</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>80</v>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>66.66666666666666</v>
       </c>
       <c r="I21" s="11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Valivarthipadu B.O</t>
+          <t>Putlacheruvu B.O</t>
         </is>
       </c>
       <c r="B22" s="13" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C22" s="13" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
@@ -4278,13 +4278,13 @@
         <v>300</v>
       </c>
       <c r="G22" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>79.2</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23">
@@ -4294,13 +4294,13 @@
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C23" s="13" t="n">
         <v>53</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
@@ -4311,29 +4311,29 @@
         <v>300</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>79.2</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="I23" s="11" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Bommuluru B.O</t>
+          <t>Valivarthipadu B.O</t>
         </is>
       </c>
       <c r="B24" s="13" t="n">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
@@ -4344,29 +4344,29 @@
         <v>300</v>
       </c>
       <c r="G24" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>77.60000000000001</v>
+        <v>66</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Nandigamalanka B.O</t>
+          <t>Bommuluru B.O</t>
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
@@ -4377,29 +4377,29 @@
         <v>300</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>74.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="I25" s="11" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Lingavaram B.O</t>
+          <t>Nandigamalanka B.O</t>
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C26" s="13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
@@ -4410,29 +4410,29 @@
         <v>300</v>
       </c>
       <c r="G26" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>72.8</v>
+        <v>62</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Ingilipakalanka B.O</t>
+          <t>Lingavaram B.O</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
         <v>111</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
@@ -4443,29 +4443,29 @@
         <v>300</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>70.39999999999999</v>
+        <v>60.66666666666667</v>
       </c>
       <c r="I27" s="11" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Vadali B.O</t>
+          <t>Ingilipakalanka B.O</t>
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="C28" s="13" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
@@ -4476,29 +4476,29 @@
         <v>300</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>69.59999999999999</v>
+        <v>58.66666666666666</v>
       </c>
       <c r="I28" s="11" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Tenneru B.O</t>
+          <t>Vadali B.O</t>
         </is>
       </c>
       <c r="B29" s="13" t="n">
-        <v>245</v>
+        <v>121</v>
       </c>
       <c r="C29" s="13" t="n">
-        <v>159</v>
+        <v>34</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
@@ -4509,29 +4509,29 @@
         <v>300</v>
       </c>
       <c r="G29" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>68.8</v>
+        <v>57.99999999999999</v>
       </c>
       <c r="I29" s="11" t="n">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>Unikili B.O</t>
+          <t>Nandivada B.O</t>
         </is>
       </c>
       <c r="B30" s="13" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C30" s="13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
@@ -4542,29 +4542,29 @@
         <v>300</v>
       </c>
       <c r="G30" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>58.4</v>
+        <v>55.33333333333334</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Komaravolu B.O</t>
+          <t>Tummalapalli B.O</t>
         </is>
       </c>
       <c r="B31" s="13" t="n">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
@@ -4575,260 +4575,260 @@
         <v>300</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>58.4</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="I31" s="11" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
+          <t>Tenneru B.O</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="n">
+        <v>246</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>171</v>
+      </c>
+      <c r="D32" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="G32" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I32" s="11" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Unikili B.O</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H33" s="19" t="n">
+        <v>48.66666666666667</v>
+      </c>
+      <c r="I33" s="11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Komaravolu B.O</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>158</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>73</v>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H34" s="19" t="n">
+        <v>48.66666666666667</v>
+      </c>
+      <c r="I34" s="11" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
           <t>Ponukumadu B.O</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n">
+      <c r="B35" s="17" t="n">
         <v>94</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C35" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="D32" s="14" t="n">
+      <c r="D35" s="18" t="n">
         <v>72</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G32" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H32" s="15" t="n">
-        <v>57.59999999999999</v>
-      </c>
-      <c r="I32" s="11" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H35" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Pedavirivada B.O</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n">
+      <c r="B36" s="17" t="n">
         <v>77</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C36" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D36" s="18" t="n">
         <v>70</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="I33" s="11" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Gandhi Asramam B.O</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n">
-        <v>77</v>
-      </c>
-      <c r="C34" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <v>70</v>
-      </c>
-      <c r="E34" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>56.00000000000001</v>
-      </c>
-      <c r="I34" s="11" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Nandivada B.O</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="n">
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H36" s="19" t="n">
+        <v>46.66666666666666</v>
+      </c>
+      <c r="I36" s="11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Guntakoduru B.O</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>83</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="D37" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H37" s="19" t="n">
+        <v>44</v>
+      </c>
+      <c r="I37" s="11" t="n">
         <v>84</v>
       </c>
-      <c r="C35" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="D35" s="14" t="n">
-        <v>68</v>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>54.40000000000001</v>
-      </c>
-      <c r="I35" s="11" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>Guntakoduru B.O</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n">
-        <v>83</v>
-      </c>
-      <c r="C36" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <v>66</v>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G36" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="I36" s="11" t="n">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Addada B.O</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n">
+      <c r="B38" s="17" t="n">
         <v>99</v>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C38" s="17" t="n">
         <v>34</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D38" s="18" t="n">
         <v>65</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G37" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>52</v>
-      </c>
-      <c r="I37" s="11" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>Pedakamanapudi B.O</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n">
-        <v>95</v>
-      </c>
-      <c r="C38" s="13" t="n">
-        <v>31</v>
-      </c>
-      <c r="D38" s="14" t="n">
-        <v>64</v>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>300</v>
-      </c>
-      <c r="G38" s="13" t="n">
-        <v>125</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>51.2</v>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H38" s="19" t="n">
+        <v>43.33333333333334</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Lakshminarasimhapuram B.O</t>
+          <t>Pedakamanapudi B.O</t>
         </is>
       </c>
       <c r="B39" s="17" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C39" s="17" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D39" s="18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
@@ -4839,62 +4839,62 @@
         <v>300</v>
       </c>
       <c r="G39" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>49.6</v>
+        <v>42.66666666666667</v>
       </c>
       <c r="I39" s="11" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>Ponukumada B.O</t>
+          <t>Lakshminarasimhapuram B.O</t>
         </is>
       </c>
       <c r="B40" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D40" s="18" t="n">
+        <v>63</v>
+      </c>
+      <c r="E40" s="16" t="inlineStr">
+        <is>
+          <t>BO</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="H40" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="I40" s="11" t="n">
         <v>87</v>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D40" s="18" t="n">
-        <v>58</v>
-      </c>
-      <c r="E40" s="16" t="inlineStr">
-        <is>
-          <t>BO</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="n">
-        <v>300</v>
-      </c>
-      <c r="G40" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="H40" s="19" t="n">
-        <v>46.40000000000001</v>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Chinaparupudi B.O</t>
+          <t>Dondapadu B.O</t>
         </is>
       </c>
       <c r="B41" s="17" t="n">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="C41" s="17" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D41" s="18" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
@@ -4905,29 +4905,29 @@
         <v>300</v>
       </c>
       <c r="G41" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>44</v>
+        <v>40.66666666666666</v>
       </c>
       <c r="I41" s="11" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>Tummalapalli B.O</t>
+          <t>Serikalavapudi B.O</t>
         </is>
       </c>
       <c r="B42" s="17" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C42" s="17" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D42" s="18" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
@@ -4938,29 +4938,29 @@
         <v>300</v>
       </c>
       <c r="G42" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H42" s="19" t="n">
-        <v>44</v>
+        <v>39.33333333333333</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>70</v>
+        <v>91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Veldipadu B.O</t>
+          <t>Ponukumada B.O</t>
         </is>
       </c>
       <c r="B43" s="17" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C43" s="17" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D43" s="18" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
@@ -4971,29 +4971,29 @@
         <v>300</v>
       </c>
       <c r="G43" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>42.4</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I43" s="11" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Lankapalli Agraharam B.O</t>
+          <t>Chinaparupudi B.O</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D44" s="18" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
@@ -5004,29 +5004,29 @@
         <v>300</v>
       </c>
       <c r="G44" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H44" s="19" t="n">
-        <v>41.6</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>Dondapadu B.O</t>
+          <t>Veldipadu B.O</t>
         </is>
       </c>
       <c r="B45" s="17" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C45" s="17" t="n">
         <v>36</v>
       </c>
       <c r="D45" s="18" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
@@ -5037,29 +5037,29 @@
         <v>300</v>
       </c>
       <c r="G45" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H45" s="19" t="n">
-        <v>40</v>
+        <v>35.33333333333334</v>
       </c>
       <c r="I45" s="11" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Nuzella B.O</t>
+          <t>Lankapalli Agraharam B.O</t>
         </is>
       </c>
       <c r="B46" s="17" t="n">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="C46" s="17" t="n">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="D46" s="18" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
@@ -5070,13 +5070,13 @@
         <v>300</v>
       </c>
       <c r="G46" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H46" s="19" t="n">
-        <v>39.2</v>
+        <v>34.66666666666667</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47">
@@ -5086,13 +5086,13 @@
         </is>
       </c>
       <c r="B47" s="17" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C47" s="17" t="n">
         <v>17</v>
       </c>
       <c r="D47" s="18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
@@ -5103,29 +5103,29 @@
         <v>300</v>
       </c>
       <c r="G47" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>38.4</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="I47" s="11" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>Edulamaddali B.O</t>
+          <t>Nuzella B.O</t>
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C48" s="17" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D48" s="18" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
@@ -5136,13 +5136,13 @@
         <v>300</v>
       </c>
       <c r="G48" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H48" s="19" t="n">
-        <v>37.6</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49">
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="B49" s="17" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C49" s="17" t="n">
         <v>85</v>
       </c>
       <c r="D49" s="18" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
@@ -5169,29 +5169,29 @@
         <v>300</v>
       </c>
       <c r="G49" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>37.6</v>
+        <v>32</v>
       </c>
       <c r="I49" s="11" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>Chinapalaparru B.O</t>
+          <t>Edulamaddali B.O</t>
         </is>
       </c>
       <c r="B50" s="17" t="n">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="C50" s="17" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="D50" s="18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
@@ -5202,29 +5202,29 @@
         <v>300</v>
       </c>
       <c r="G50" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H50" s="19" t="n">
-        <v>36</v>
+        <v>30.66666666666666</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Vanapumala B.O</t>
+          <t>Chinapalaparru B.O</t>
         </is>
       </c>
       <c r="B51" s="17" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C51" s="17" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D51" s="18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
@@ -5235,26 +5235,26 @@
         <v>300</v>
       </c>
       <c r="G51" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>35.2</v>
+        <v>30</v>
       </c>
       <c r="I51" s="11" t="n">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>Pedaparupudi B.O</t>
+          <t>Vanapumala B.O</t>
         </is>
       </c>
       <c r="B52" s="17" t="n">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C52" s="17" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D52" s="18" t="n">
         <v>44</v>
@@ -5268,29 +5268,29 @@
         <v>300</v>
       </c>
       <c r="G52" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H52" s="19" t="n">
-        <v>35.2</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>Guraza B.O</t>
+          <t>Pedaparupudi B.O</t>
         </is>
       </c>
       <c r="B53" s="17" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C53" s="17" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D53" s="18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
@@ -5301,26 +5301,26 @@
         <v>300</v>
       </c>
       <c r="G53" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H53" s="19" t="n">
-        <v>33.6</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="I53" s="11" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>Komarru B.O</t>
+          <t>Guraza B.O</t>
         </is>
       </c>
       <c r="B54" s="17" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C54" s="17" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D54" s="18" t="n">
         <v>42</v>
@@ -5334,29 +5334,29 @@
         <v>300</v>
       </c>
       <c r="G54" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H54" s="19" t="n">
-        <v>33.6</v>
+        <v>28</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>83</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>Polukonda B.O</t>
+          <t>Komarru B.O</t>
         </is>
       </c>
       <c r="B55" s="17" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C55" s="17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D55" s="18" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
@@ -5367,29 +5367,29 @@
         <v>300</v>
       </c>
       <c r="G55" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>32.8</v>
+        <v>28</v>
       </c>
       <c r="I55" s="11" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>Serigolvepalli B.O</t>
+          <t>Polukonda B.O</t>
         </is>
       </c>
       <c r="B56" s="17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C56" s="17" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D56" s="18" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
@@ -5400,26 +5400,26 @@
         <v>300</v>
       </c>
       <c r="G56" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H56" s="19" t="n">
-        <v>31.2</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>86</v>
+        <v>109</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>Serikalavapudi B.O</t>
+          <t>Serigolvepalli B.O</t>
         </is>
       </c>
       <c r="B57" s="17" t="n">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C57" s="17" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D57" s="18" t="n">
         <v>39</v>
@@ -5433,26 +5433,26 @@
         <v>300</v>
       </c>
       <c r="G57" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>31.2</v>
+        <v>26</v>
       </c>
       <c r="I57" s="11" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>Peruru B.O</t>
+          <t>Chinayerukapadu B.O</t>
         </is>
       </c>
       <c r="B58" s="17" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C58" s="17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D58" s="18" t="n">
         <v>39</v>
@@ -5466,29 +5466,29 @@
         <v>300</v>
       </c>
       <c r="G58" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H58" s="19" t="n">
-        <v>31.2</v>
+        <v>26</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>Chinayerukapadu B.O</t>
+          <t>Peruru B.O</t>
         </is>
       </c>
       <c r="B59" s="17" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C59" s="17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D59" s="18" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -5499,29 +5499,29 @@
         <v>300</v>
       </c>
       <c r="G59" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I59" s="11" t="n">
-        <v>90</v>
+        <v>111</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>Amudalapalli B.O</t>
+          <t>Lingala B.O</t>
         </is>
       </c>
       <c r="B60" s="17" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="C60" s="17" t="n">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="D60" s="18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
@@ -5532,29 +5532,29 @@
         <v>300</v>
       </c>
       <c r="G60" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H60" s="19" t="n">
-        <v>24.8</v>
+        <v>22</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>94</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>Lingala B.O</t>
+          <t>Amudalapalli B.O</t>
         </is>
       </c>
       <c r="B61" s="17" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="C61" s="17" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="D61" s="18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -5565,13 +5565,13 @@
         <v>300</v>
       </c>
       <c r="G61" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>24</v>
+        <v>20.66666666666667</v>
       </c>
       <c r="I61" s="11" t="n">
-        <v>95</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62">
@@ -5581,13 +5581,13 @@
         </is>
       </c>
       <c r="B62" s="17" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C62" s="17" t="n">
         <v>5</v>
       </c>
       <c r="D62" s="18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -5598,13 +5598,13 @@
         <v>300</v>
       </c>
       <c r="G62" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H62" s="19" t="n">
-        <v>20.8</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="I62" s="11" t="n">
-        <v>99</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63">
@@ -5631,13 +5631,13 @@
         <v>300</v>
       </c>
       <c r="G63" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="I63" s="11" t="n">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64">
@@ -5664,29 +5664,29 @@
         <v>300</v>
       </c>
       <c r="G64" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H64" s="19" t="n">
-        <v>18.4</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>102</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>Vempadu B.O</t>
+          <t>Kudaravalli B.O</t>
         </is>
       </c>
       <c r="B65" s="17" t="n">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="C65" s="17" t="n">
-        <v>97</v>
+        <v>48</v>
       </c>
       <c r="D65" s="18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
@@ -5697,29 +5697,29 @@
         <v>300</v>
       </c>
       <c r="G65" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H65" s="19" t="n">
-        <v>15.2</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="I65" s="11" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>Kudaravalli B.O</t>
+          <t>Vempadu B.O</t>
         </is>
       </c>
       <c r="B66" s="17" t="n">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="C66" s="17" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D66" s="18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5730,13 +5730,13 @@
         <v>300</v>
       </c>
       <c r="G66" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H66" s="19" t="n">
-        <v>14.4</v>
+        <v>12.66666666666667</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>107</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67">
@@ -5763,13 +5763,13 @@
         <v>300</v>
       </c>
       <c r="G67" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>14.4</v>
+        <v>12</v>
       </c>
       <c r="I67" s="11" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68">
@@ -5779,13 +5779,13 @@
         </is>
       </c>
       <c r="B68" s="17" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C68" s="17" t="n">
         <v>36</v>
       </c>
       <c r="D68" s="18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
@@ -5796,13 +5796,13 @@
         <v>300</v>
       </c>
       <c r="G68" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H68" s="19" t="n">
-        <v>7.199999999999999</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>116</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69">
@@ -5829,13 +5829,13 @@
         <v>300</v>
       </c>
       <c r="G69" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I69" s="11" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70">
@@ -5862,13 +5862,13 @@
         <v>300</v>
       </c>
       <c r="G70" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>-0.8</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="71">
@@ -5895,13 +5895,13 @@
         <v>300</v>
       </c>
       <c r="G71" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>-4.8</v>
+        <v>-4</v>
       </c>
       <c r="I71" s="11" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72">
@@ -5914,10 +5914,10 @@
         <v>250</v>
       </c>
       <c r="C72" s="17" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -5928,13 +5928,13 @@
         <v>300</v>
       </c>
       <c r="G72" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H72" s="19" t="n">
-        <v>-5.600000000000001</v>
+        <v>-5.333333333333334</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73">
@@ -5961,13 +5961,13 @@
         <v>300</v>
       </c>
       <c r="G73" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-23.2</v>
+        <v>-19.33333333333333</v>
       </c>
       <c r="I73" s="11" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -6051,13 +6051,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         <v>600</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>149.6</v>
+        <v>124</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6101,10 +6101,10 @@
         <v>600</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>133.2</v>
+        <v>111</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6134,79 +6134,79 @@
         <v>600</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>124</v>
+        <v>103.3333333333333</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Rudrapaka S.O</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="8" t="n">
         <v>302</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="9" t="n">
         <v>268</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>107.2</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0</v>
+      <c r="G5" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>89.33333333333333</v>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Mudunuru S.O</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="8" t="n">
         <v>335</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="8" t="n">
         <v>72</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="9" t="n">
         <v>263</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="8" t="n">
         <v>600</v>
       </c>
-      <c r="G6" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>105.2</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0</v>
+      <c r="G6" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>87.66666666666667</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="7">
@@ -6233,46 +6233,46 @@
         <v>600</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Mudinepalli S.O</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
-        <v>486</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>258</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>228</v>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="B8" s="13" t="n">
+        <v>490</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>230</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="13" t="n">
         <v>600</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>91.2</v>
+      <c r="G8" s="13" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>76.66666666666667</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -6285,10 +6285,10 @@
         <v>223</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
@@ -6299,13 +6299,13 @@
         <v>600</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>78.8</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="I9" s="11" t="n">
-        <v>53</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -6332,95 +6332,95 @@
         <v>600</v>
       </c>
       <c r="G10" s="13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>63.6</v>
+        <v>53</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>91</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Indupalli S.O</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>275</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>127</v>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>148</v>
+      </c>
+      <c r="E11" s="16" t="inlineStr">
+        <is>
+          <t>SO</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>600</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>49.33333333333334</v>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Rajendranagar Colony S.O</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>353</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>205</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>148</v>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="B12" s="17" t="n">
+        <v>354</v>
+      </c>
+      <c r="C12" s="17" t="n">
+        <v>212</v>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>142</v>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>SO</t>
         </is>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F12" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="G11" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Golvepalli (Zami) S.O</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>143</v>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>130</v>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>SO</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="n">
-        <v>600</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>52</v>
+      <c r="G12" s="17" t="n">
+        <v>300</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>47.33333333333334</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Tamirisa S.O</t>
+          <t>Golvepalli (Zami) S.O</t>
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
@@ -6431,29 +6431,29 @@
         <v>600</v>
       </c>
       <c r="G13" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>46.40000000000001</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="I13" s="11" t="n">
-        <v>134</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Janardhanapuram S.O</t>
+          <t>Tamirisa S.O</t>
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
@@ -6464,29 +6464,29 @@
         <v>600</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H14" s="19" t="n">
-        <v>43.2</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Indupalli S.O</t>
+          <t>Janardhanapuram S.O</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="D15" s="18" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
@@ -6497,13 +6497,13 @@
         <v>600</v>
       </c>
       <c r="G15" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>39.2</v>
+        <v>37</v>
       </c>
       <c r="I15" s="11" t="n">
-        <v>152</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16">
@@ -6513,13 +6513,13 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="17" t="n">
         <v>57</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
@@ -6530,13 +6530,13 @@
         <v>600</v>
       </c>
       <c r="G16" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H16" s="19" t="n">
-        <v>24.8</v>
+        <v>21</v>
       </c>
       <c r="I16" s="11" t="n">
-        <v>188</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -6614,36 +6614,36 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Gudivada H.O</t>
         </is>
       </c>
-      <c r="B2" s="13" t="n">
-        <v>1245</v>
-      </c>
-      <c r="C2" s="13" t="n">
-        <v>807</v>
-      </c>
-      <c r="D2" s="14" t="n">
-        <v>438</v>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="B2" s="17" t="n">
+        <v>1255</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>810</v>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>445</v>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>HO</t>
         </is>
       </c>
-      <c r="F2" s="13" t="n">
+      <c r="F2" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="G2" s="13" t="n">
-        <v>833.3333333333334</v>
-      </c>
-      <c r="H2" s="15" t="n">
-        <v>52.56</v>
+      <c r="G2" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>44.5</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>395.3333333333334</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -6723,17 +6723,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Appikatla B.O</t>
+          <t>Vennanapudi B.O</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>252</v>
+        <v>309</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -6744,10 +6744,10 @@
         <v>300</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>156</v>
+        <v>131.3333333333333</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -6756,17 +6756,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Vennanapudi B.O</t>
+          <t>Appikatla B.O</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>112</v>
+        <v>57</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -6777,10 +6777,10 @@
         <v>300</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>153.6</v>
+        <v>130</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -6793,13 +6793,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>34</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -6810,13 +6810,13 @@
         <v>300</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>117.6</v>
+        <v>98.66666666666667</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -6843,29 +6843,29 @@
         <v>300</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>112.8</v>
+        <v>94</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Dosapadu B.O</t>
+          <t>Bhushanagulla B.O</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -6876,13 +6876,13 @@
         <v>300</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>111.2</v>
+        <v>93.33333333333333</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -6983,13 +6983,13 @@
         <v>300</v>
       </c>
       <c r="G2" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>-23.2</v>
+        <v>-19.33333333333333</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>154</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
@@ -7002,10 +7002,10 @@
         <v>250</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7016,13 +7016,13 @@
         <v>300</v>
       </c>
       <c r="G3" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>-5.600000000000001</v>
+        <v>-5.333333333333334</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
@@ -7049,13 +7049,13 @@
         <v>300</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>-4.8</v>
+        <v>-4</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>131</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5">
@@ -7082,13 +7082,13 @@
         <v>300</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>-0.8</v>
+        <v>-0.6666666666666667</v>
       </c>
       <c r="I5" s="11" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
@@ -7115,13 +7115,13 @@
         <v>300</v>
       </c>
       <c r="G6" s="17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="H6" s="19" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -7205,13 +7205,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -7222,10 +7222,10 @@
         <v>600</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>149.6</v>
+        <v>124</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
@@ -7255,10 +7255,10 @@
         <v>600</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>133.2</v>
+        <v>111</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
@@ -7288,10 +7288,10 @@
         <v>600</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>124</v>
+        <v>103.3333333333333</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B2" s="17" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C2" s="17" t="n">
         <v>57</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
@@ -7395,29 +7395,29 @@
         <v>600</v>
       </c>
       <c r="G2" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H2" s="19" t="n">
-        <v>24.8</v>
+        <v>21</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>188</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>Indupalli S.O</t>
+          <t>Janardhanapuram S.O</t>
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="C3" s="17" t="n">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="D3" s="18" t="n">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -7428,29 +7428,29 @@
         <v>600</v>
       </c>
       <c r="G3" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>39.2</v>
+        <v>37</v>
       </c>
       <c r="I3" s="11" t="n">
-        <v>152</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>Janardhanapuram S.O</t>
+          <t>Tamirisa S.O</t>
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
@@ -7461,13 +7461,13 @@
         <v>600</v>
       </c>
       <c r="G4" s="17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H4" s="19" t="n">
-        <v>43.2</v>
+        <v>38.66666666666666</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B2" s="20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>13521</v>
+        <v>13746</v>
       </c>
     </row>
     <row r="8">
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>5020</v>
+        <v>5058</v>
       </c>
     </row>
     <row r="9">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>8501</v>
+        <v>8688</v>
       </c>
     </row>
   </sheetData>
